--- a/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_H_TVPSOF-CSTD-0-01-A-C0.xlsx
+++ b/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_H_TVPSOF-CSTD-0-01-A-C0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\mainline\ren_d1x\src\IpcApplication\Vom\Alert\matrix-CSTD-1-03-A-C0\scc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\BEV\BEV設計・実装\課題管理一覧\フレーム変更漏れ対応\Alertパラメータ設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1F5A6A5-9A7D-4E3D-BC4E-FEE1D0303C60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96816E15-94FE-44EB-9BFC-8CA53126DD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25974" yWindow="-109" windowWidth="26301" windowHeight="14305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -2614,14 +2614,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>PMN1G03</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>PMN1G03_STS</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ALERT_CH_H_TVPSOF</t>
   </si>
   <si>
@@ -2921,6 +2913,14 @@
   </si>
   <si>
     <t>https://aip01.dndev.net/svn/met/toyota/std/rd/spec/19PFver3/tags/00.Product/v0.0.d/%E5%88%B6%E5%BE%A1%E4%BB%95%E6%A7%98/MET-H_TVPSOF-CSTD-0-01-A-C0/MET-H_TVPSOF-CSTD-0-01-A-C0.xlsm</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>BDC1S33_STS</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>BDC1S33</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -4967,37 +4967,16 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5042,10 +5021,31 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5092,7 +5092,7 @@
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill>
@@ -5138,16 +5138,6 @@
       <font>
         <color rgb="FFFF0000"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFF00"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -6103,8 +6093,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="13390774" y="161925"/>
-          <a:ext cx="38168595" cy="16573047"/>
+          <a:off x="13233701" y="163902"/>
+          <a:ext cx="38884887" cy="16748331"/>
           <a:chOff x="13193924" y="163286"/>
           <a:chExt cx="38059284" cy="16837025"/>
         </a:xfrm>
@@ -8244,6 +8234,282 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>414068</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>60385</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>405441</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>83219</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DAD00625-DB4C-459F-A1C7-22816EDECA01}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20366966" y="11973464"/>
+          <a:ext cx="1854679" cy="842344"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>543464</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>103517</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>312073</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>123306</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="線吹き出し 1 (枠付き) 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41FC53C5-551F-4134-931E-2349ED0DC192}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13664241" y="11033185"/>
+          <a:ext cx="2253017" cy="1167102"/>
+        </a:xfrm>
+        <a:prstGeom prst="borderCallout1">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 52087"/>
+            <a:gd name="adj2" fmla="val 100142"/>
+            <a:gd name="adj3" fmla="val 105367"/>
+            <a:gd name="adj4" fmla="val 297769"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>仕様の表記が誤っているが</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>BA</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>表より以下となる。</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>〇「</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>BDC1S33</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>」</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>✖「</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>PMN1G03</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>」</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -8536,13 +8802,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B2:R13"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="1" max="1" width="4.453125" customWidth="1"/>
+    <col min="1" max="1" width="4.5" customWidth="1"/>
     <col min="2" max="2" width="9" style="9" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="69.453125" customWidth="1"/>
-    <col min="5" max="6" width="12.90625" customWidth="1"/>
-    <col min="7" max="18" width="13.08984375" customWidth="1"/>
+    <col min="4" max="4" width="69.5" customWidth="1"/>
+    <col min="5" max="6" width="12.875" customWidth="1"/>
+    <col min="7" max="18" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="25.5" customHeight="1">
@@ -8612,7 +8878,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:18" ht="13.5" thickBot="1"/>
+    <row r="6" spans="2:18" ht="13.6" thickBot="1"/>
     <row r="7" spans="2:18">
       <c r="C7" s="238" t="s">
         <v>0</v>
@@ -8692,7 +8958,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:18" ht="13.5" thickTop="1">
+    <row r="9" spans="2:18" ht="13.6" thickTop="1">
       <c r="B9" s="9">
         <f>IF(C9=0,0,ROW()-ROW($B$8))</f>
         <v>1</v>
@@ -8738,16 +9004,16 @@
         <v>44162</v>
       </c>
     </row>
-    <row r="10" spans="2:18" ht="78">
+    <row r="10" spans="2:18" ht="77.45">
       <c r="B10" s="9">
         <f t="shared" ref="B10:B13" si="0">IF(C10=0,0,ROW()-ROW($B$8))</f>
         <v>2</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D10" s="222" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>31</v>
@@ -8778,22 +9044,22 @@
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="R10" s="223">
         <v>44280</v>
       </c>
     </row>
-    <row r="11" spans="2:18" ht="143">
+    <row r="11" spans="2:18" ht="142">
       <c r="B11" s="9">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D11" s="222" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>31</v>
@@ -8824,7 +9090,7 @@
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="R11" s="223">
         <v>44573</v>
@@ -8836,16 +9102,16 @@
         <v>4</v>
       </c>
       <c r="C12" s="233" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D12" s="234" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E12" s="235" t="s">
         <v>133</v>
       </c>
       <c r="F12" s="236" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G12" s="235" t="s">
         <v>31</v>
@@ -8860,7 +9126,7 @@
         <v>31</v>
       </c>
       <c r="K12" s="235" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="L12" s="237">
         <v>45345</v>
@@ -8884,7 +9150,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="2:18" ht="13.5" thickBot="1">
+    <row r="13" spans="2:18" ht="13.6" thickBot="1">
       <c r="B13" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -8928,11 +9194,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:E39"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="2" max="2" width="4.6328125" customWidth="1"/>
-    <col min="3" max="3" width="3.453125" customWidth="1"/>
-    <col min="4" max="4" width="17.453125" customWidth="1"/>
+    <col min="2" max="2" width="4.625" customWidth="1"/>
+    <col min="3" max="3" width="3.5" customWidth="1"/>
+    <col min="4" max="4" width="17.5" customWidth="1"/>
     <col min="5" max="5" width="106" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8946,13 +9212,13 @@
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="13.5" thickBot="1">
+    <row r="6" spans="2:5" ht="13.6" thickBot="1">
       <c r="B6" s="160" t="s">
         <v>136</v>
       </c>
       <c r="C6" s="160"/>
     </row>
-    <row r="7" spans="2:5" ht="13.5" thickBot="1">
+    <row r="7" spans="2:5" ht="13.6" thickBot="1">
       <c r="C7" s="81" t="s">
         <v>138</v>
       </c>
@@ -8969,7 +9235,7 @@
         <v>147</v>
       </c>
       <c r="E8" s="163" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -8977,7 +9243,7 @@
       <c r="D9" s="172"/>
       <c r="E9" s="171"/>
     </row>
-    <row r="10" spans="2:5" ht="13.5" thickBot="1">
+    <row r="10" spans="2:5" ht="13.6" thickBot="1">
       <c r="C10" s="168"/>
       <c r="D10" s="92"/>
       <c r="E10" s="5"/>
@@ -8985,14 +9251,14 @@
     <row r="11" spans="2:5">
       <c r="C11" s="166"/>
     </row>
-    <row r="12" spans="2:5" ht="13.5" thickBot="1">
+    <row r="12" spans="2:5" ht="13.6" thickBot="1">
       <c r="B12" s="161" t="s">
         <v>137</v>
       </c>
       <c r="C12" s="88"/>
       <c r="D12" s="88"/>
     </row>
-    <row r="13" spans="2:5" ht="13.5" thickBot="1">
+    <row r="13" spans="2:5" ht="13.6" thickBot="1">
       <c r="B13" s="162"/>
       <c r="C13" s="167" t="s">
         <v>138</v>
@@ -9004,7 +9270,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="13.5" thickTop="1">
+    <row r="14" spans="2:5" ht="13.6" thickTop="1">
       <c r="C14" s="164">
         <v>0</v>
       </c>
@@ -9081,17 +9347,17 @@
         <v>186</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="13.5" thickBot="1">
+    <row r="21" spans="2:5" ht="13.6" thickBot="1">
       <c r="C21" s="168"/>
       <c r="D21" s="92"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="24" spans="2:5" ht="13.5" thickBot="1">
+    <row r="24" spans="2:5" ht="13.6" thickBot="1">
       <c r="B24" s="160" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="13.5" thickBot="1">
+    <row r="25" spans="2:5" ht="13.6" thickBot="1">
       <c r="C25" s="167" t="s">
         <v>138</v>
       </c>
@@ -9113,7 +9379,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="27" spans="2:5" ht="120" customHeight="1">
+    <row r="27" spans="2:5" ht="120.1" customHeight="1">
       <c r="C27" s="165">
         <v>1</v>
       </c>
@@ -9178,12 +9444,12 @@
       <c r="D33" s="91"/>
       <c r="E33" s="78"/>
     </row>
-    <row r="34" spans="2:5" ht="13.5" thickBot="1">
+    <row r="34" spans="2:5" ht="13.6" thickBot="1">
       <c r="C34" s="168"/>
       <c r="D34" s="92"/>
       <c r="E34" s="5"/>
     </row>
-    <row r="37" spans="2:5" ht="13.5" thickBot="1">
+    <row r="37" spans="2:5" ht="13.6" thickBot="1">
       <c r="B37" s="160" t="s">
         <v>182</v>
       </c>
@@ -9195,7 +9461,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="13.5" thickBot="1">
+    <row r="39" spans="2:5" ht="13.6" thickBot="1">
       <c r="C39" s="249"/>
       <c r="D39" s="250"/>
       <c r="E39" s="5" t="s">
@@ -9222,131 +9488,131 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:N37"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="2" max="2" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="26.90625" customWidth="1"/>
-    <col min="9" max="9" width="20.90625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="3.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="26.875" customWidth="1"/>
+    <col min="9" max="9" width="20.875" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="13.5" thickBot="1"/>
+    <row r="1" spans="2:14" ht="13.6" thickBot="1"/>
     <row r="2" spans="2:14">
-      <c r="B2" s="276" t="s">
+      <c r="B2" s="251" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="277"/>
-      <c r="D2" s="264" t="s">
-        <v>262</v>
-      </c>
-      <c r="E2" s="265"/>
-      <c r="F2" s="265"/>
-      <c r="G2" s="265"/>
-      <c r="H2" s="266"/>
+      <c r="C2" s="252"/>
+      <c r="D2" s="257" t="s">
+        <v>260</v>
+      </c>
+      <c r="E2" s="258"/>
+      <c r="F2" s="258"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259"/>
     </row>
     <row r="3" spans="2:14">
-      <c r="B3" s="251" t="s">
+      <c r="B3" s="253" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="252"/>
-      <c r="D3" s="267" t="s">
-        <v>273</v>
-      </c>
-      <c r="E3" s="268"/>
-      <c r="F3" s="268"/>
-      <c r="G3" s="268"/>
-      <c r="H3" s="269"/>
-    </row>
-    <row r="4" spans="2:14" ht="13.5" thickBot="1">
-      <c r="B4" s="262" t="s">
+      <c r="C3" s="254"/>
+      <c r="D3" s="260" t="s">
+        <v>271</v>
+      </c>
+      <c r="E3" s="261"/>
+      <c r="F3" s="261"/>
+      <c r="G3" s="261"/>
+      <c r="H3" s="262"/>
+    </row>
+    <row r="4" spans="2:14" ht="13.6" thickBot="1">
+      <c r="B4" s="255" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="263"/>
-      <c r="D4" s="270" t="str">
+      <c r="C4" s="256"/>
+      <c r="D4" s="263" t="str">
         <f ca="1">表紙!D3&amp;".c"</f>
         <v>alert_H_TVPSOF-CSTD-0-01-A-C0.c</v>
       </c>
-      <c r="E4" s="271"/>
-      <c r="F4" s="271"/>
-      <c r="G4" s="271"/>
-      <c r="H4" s="272"/>
-    </row>
-    <row r="5" spans="2:14" ht="13.5" thickBot="1">
+      <c r="E4" s="264"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="265"/>
+    </row>
+    <row r="5" spans="2:14" ht="13.6" thickBot="1">
       <c r="D5" t="str">
         <f ca="1">IF(LEN(表紙!D3&amp;".c") = LENB(表紙!D3&amp;".c"),"※モジュール名 全角チェックOK","※モジュール名 全角チェックNG：ファイル名に全角文字が使用されています！")</f>
         <v>※モジュール名 全角チェックOK</v>
       </c>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="276" t="s">
+      <c r="B6" s="251" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="277"/>
-      <c r="D6" s="273" t="str">
+      <c r="C6" s="252"/>
+      <c r="D6" s="266" t="str">
         <f ca="1">MID(D4, LEN("alert_") + 1, FIND("-",D4,1) - LEN("alert_") - 1)</f>
         <v>H_TVPSOF</v>
       </c>
-      <c r="E6" s="274"/>
-      <c r="F6" s="274"/>
-      <c r="G6" s="274"/>
-      <c r="H6" s="275"/>
+      <c r="E6" s="267"/>
+      <c r="F6" s="267"/>
+      <c r="G6" s="267"/>
+      <c r="H6" s="268"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="251" t="s">
+      <c r="B7" s="253" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="252"/>
-      <c r="D7" s="253">
+      <c r="C7" s="254"/>
+      <c r="D7" s="269">
         <f>COUNTA($D$13:$D$37)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="254"/>
-      <c r="F7" s="254"/>
-      <c r="G7" s="254"/>
-      <c r="H7" s="255"/>
+      <c r="E7" s="270"/>
+      <c r="F7" s="270"/>
+      <c r="G7" s="270"/>
+      <c r="H7" s="271"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="251" t="s">
+      <c r="B8" s="253" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="252"/>
-      <c r="D8" s="253" t="str">
+      <c r="C8" s="254"/>
+      <c r="D8" s="269" t="str">
         <f ca="1">"st_gp_ALERT_"&amp;UPPER(D6)&amp;"_MTRX"</f>
         <v>st_gp_ALERT_H_TVPSOF_MTRX</v>
       </c>
-      <c r="E8" s="254"/>
-      <c r="F8" s="254"/>
-      <c r="G8" s="254"/>
-      <c r="H8" s="255"/>
+      <c r="E8" s="270"/>
+      <c r="F8" s="270"/>
+      <c r="G8" s="270"/>
+      <c r="H8" s="271"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="251" t="s">
+      <c r="B9" s="253" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="252"/>
-      <c r="D9" s="256" t="s">
+      <c r="C9" s="254"/>
+      <c r="D9" s="272" t="s">
         <v>231</v>
       </c>
-      <c r="E9" s="257"/>
-      <c r="F9" s="257"/>
-      <c r="G9" s="257"/>
-      <c r="H9" s="258"/>
-    </row>
-    <row r="10" spans="2:14" ht="13.5" thickBot="1">
-      <c r="B10" s="262" t="s">
+      <c r="E9" s="273"/>
+      <c r="F9" s="273"/>
+      <c r="G9" s="273"/>
+      <c r="H9" s="274"/>
+    </row>
+    <row r="10" spans="2:14" ht="13.6" thickBot="1">
+      <c r="B10" s="255" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="263"/>
-      <c r="D10" s="259"/>
-      <c r="E10" s="260"/>
-      <c r="F10" s="260"/>
-      <c r="G10" s="260"/>
-      <c r="H10" s="261"/>
-    </row>
-    <row r="11" spans="2:14" ht="13.5" thickBot="1"/>
-    <row r="12" spans="2:14" ht="13.5" thickBot="1">
+      <c r="C10" s="256"/>
+      <c r="D10" s="275"/>
+      <c r="E10" s="276"/>
+      <c r="F10" s="276"/>
+      <c r="G10" s="276"/>
+      <c r="H10" s="277"/>
+    </row>
+    <row r="11" spans="2:14" ht="13.6" thickBot="1"/>
+    <row r="12" spans="2:14" ht="13.6" thickBot="1">
       <c r="B12" s="151" t="s">
         <v>34</v>
       </c>
@@ -9381,7 +9647,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="13.5" thickTop="1">
+    <row r="13" spans="2:14" ht="13.6" thickTop="1">
       <c r="B13" s="110">
         <v>1</v>
       </c>
@@ -10234,7 +10500,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:14" ht="13.5" thickBot="1">
+    <row r="37" spans="2:14" ht="13.6" thickBot="1">
       <c r="B37" s="101">
         <v>25</v>
       </c>
@@ -10275,37 +10541,37 @@
     <protectedRange sqref="D2:H3 D9:H10 C13:E37" name="編集許可"/>
   </protectedRanges>
   <mergeCells count="16">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="D9:H9"/>
     <mergeCell ref="D10:H10"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C13:C37">
-    <cfRule type="expression" dxfId="7" priority="4">
+    <cfRule type="expression" dxfId="6" priority="4">
       <formula>14&lt;LEN($D$6)+LEN($C13)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="6" priority="3">
-      <formula>14 &lt; LEN($D$6)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="NG">
       <formula>NOT(ISERROR(SEARCH("NG",D5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D6">
+    <cfRule type="expression" dxfId="4" priority="3">
+      <formula>14 &lt; LEN($D$6)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
@@ -10330,21 +10596,21 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B2:R59"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="2" max="2" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="36.453125" customWidth="1"/>
-    <col min="6" max="6" width="52.90625" customWidth="1"/>
-    <col min="7" max="7" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="15" width="3.90625" customWidth="1"/>
-    <col min="16" max="16" width="9.90625" customWidth="1"/>
-    <col min="17" max="17" width="44.6328125" customWidth="1"/>
-    <col min="18" max="18" width="73.6328125" customWidth="1"/>
+    <col min="5" max="5" width="36.5" customWidth="1"/>
+    <col min="6" max="6" width="52.875" customWidth="1"/>
+    <col min="7" max="7" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="15" width="3.875" customWidth="1"/>
+    <col min="16" max="16" width="9.875" customWidth="1"/>
+    <col min="17" max="17" width="44.625" customWidth="1"/>
+    <col min="18" max="18" width="73.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="13.5" thickBot="1">
+    <row r="2" spans="2:18" ht="13.6" thickBot="1">
       <c r="B2" t="s">
         <v>210</v>
       </c>
@@ -10352,7 +10618,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="13.5" thickBot="1">
+    <row r="3" spans="2:18" ht="13.6" thickBot="1">
       <c r="B3" s="151" t="s">
         <v>34</v>
       </c>
@@ -10390,7 +10656,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="13.5" hidden="1" thickTop="1">
+    <row r="4" spans="2:18" ht="13.6" hidden="1" thickTop="1">
       <c r="B4" s="183">
         <v>0</v>
       </c>
@@ -10418,7 +10684,7 @@
       </c>
       <c r="R4" s="146"/>
     </row>
-    <row r="5" spans="2:18" ht="13.5" thickTop="1">
+    <row r="5" spans="2:18" ht="13.6" thickTop="1">
       <c r="B5" s="186">
         <v>1</v>
       </c>
@@ -10946,7 +11212,7 @@
       <c r="Q28" s="155"/>
       <c r="R28" s="122"/>
     </row>
-    <row r="29" spans="2:18" ht="13.5" thickBot="1">
+    <row r="29" spans="2:18" ht="13.6" thickBot="1">
       <c r="B29" s="187">
         <v>25</v>
       </c>
@@ -10968,7 +11234,7 @@
       <c r="Q29" s="153"/>
       <c r="R29" s="124"/>
     </row>
-    <row r="32" spans="2:18" ht="13.5" thickBot="1">
+    <row r="32" spans="2:18" ht="13.6" thickBot="1">
       <c r="B32" t="s">
         <v>211</v>
       </c>
@@ -10976,7 +11242,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="33" spans="2:18" ht="13.5" thickBot="1">
+    <row r="33" spans="2:18" ht="13.6" thickBot="1">
       <c r="B33" s="151" t="s">
         <v>34</v>
       </c>
@@ -11008,7 +11274,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:18" ht="13.5" hidden="1" thickTop="1">
+    <row r="34" spans="2:18" ht="13.6" hidden="1" thickTop="1">
       <c r="B34" s="183">
         <v>0</v>
       </c>
@@ -11034,7 +11300,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="35" spans="2:18" ht="13.5" thickTop="1">
+    <row r="35" spans="2:18" ht="13.6" thickTop="1">
       <c r="B35" s="186">
         <v>1</v>
       </c>
@@ -11562,7 +11828,7 @@
       <c r="Q58" s="155"/>
       <c r="R58" s="188"/>
     </row>
-    <row r="59" spans="2:18" ht="13.5" thickBot="1">
+    <row r="59" spans="2:18" ht="13.6" thickBot="1">
       <c r="B59" s="187">
         <v>25</v>
       </c>
@@ -11610,29 +11876,29 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:U103"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="2" max="2" width="28.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.90625" customWidth="1"/>
-    <col min="5" max="5" width="12.36328125" customWidth="1"/>
-    <col min="6" max="6" width="19.90625" customWidth="1"/>
-    <col min="7" max="7" width="12.36328125" customWidth="1"/>
+    <col min="2" max="2" width="28.375" customWidth="1"/>
+    <col min="3" max="3" width="15.875" customWidth="1"/>
+    <col min="5" max="5" width="12.375" customWidth="1"/>
+    <col min="6" max="6" width="19.875" customWidth="1"/>
+    <col min="7" max="7" width="12.375" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="12.36328125" customWidth="1"/>
+    <col min="9" max="9" width="12.375" customWidth="1"/>
     <col min="10" max="10" width="29" customWidth="1"/>
-    <col min="11" max="11" width="12.36328125" customWidth="1"/>
-    <col min="12" max="12" width="16.08984375" customWidth="1"/>
-    <col min="14" max="14" width="30.08984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="57.08984375" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="12.375" customWidth="1"/>
+    <col min="12" max="12" width="16.125" customWidth="1"/>
+    <col min="14" max="14" width="30.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="57.125" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="13.5" thickBot="1">
+    <row r="1" spans="2:21" ht="13.6" thickBot="1">
       <c r="C1" s="94" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="13.5" thickBot="1">
+    <row r="2" spans="2:21" ht="13.6" thickBot="1">
       <c r="B2" s="102" t="s">
         <v>58</v>
       </c>
@@ -11676,7 +11942,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="2:21" ht="14" hidden="1" thickTop="1" thickBot="1">
+    <row r="3" spans="2:21" ht="14.3" hidden="1" thickTop="1" thickBot="1">
       <c r="B3" s="26"/>
       <c r="C3" s="53" t="s">
         <v>110</v>
@@ -11697,12 +11963,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="13.5" thickTop="1">
+    <row r="4" spans="2:21" ht="13.6" thickTop="1">
       <c r="B4" s="26" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C4" s="53" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D4" s="118">
         <v>0</v>
@@ -11717,13 +11983,13 @@
         <v>132</v>
       </c>
       <c r="H4" s="120" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="I4" s="119" t="s">
         <v>132</v>
       </c>
       <c r="J4" s="120" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="K4" s="119" t="s">
         <v>132</v>
@@ -11965,7 +12231,7 @@
       </c>
       <c r="U12" s="31"/>
     </row>
-    <row r="13" spans="2:21" ht="13.5" thickBot="1">
+    <row r="13" spans="2:21" ht="13.6" thickBot="1">
       <c r="B13" s="26"/>
       <c r="C13" s="25"/>
       <c r="D13" s="121"/>
@@ -14216,7 +14482,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="2:15" ht="13.5" thickBot="1">
+    <row r="103" spans="2:15" ht="13.6" thickBot="1">
       <c r="B103" s="55"/>
       <c r="C103" s="56"/>
       <c r="D103" s="123"/>
@@ -14247,12 +14513,7 @@
     <protectedRange sqref="B4:L103" name="範囲1"/>
   </protectedRanges>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="M4:M103">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
-      <formula>32</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M3">
+  <conditionalFormatting sqref="M3:M103">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
       <formula>32</formula>
     </cfRule>
@@ -14291,18 +14552,18 @@
     <tabColor rgb="FFCCECFF"/>
   </sheetPr>
   <dimension ref="A1:AW199"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="16.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
     <col min="4" max="35" width="3" customWidth="1"/>
-    <col min="36" max="36" width="36.36328125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.08984375" customWidth="1"/>
+    <col min="36" max="36" width="36.375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.125" customWidth="1"/>
     <col min="38" max="42" width="9" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="20.6328125" hidden="1" customWidth="1"/>
-    <col min="44" max="47" width="41.08984375" customWidth="1"/>
-    <col min="48" max="48" width="23.6328125" customWidth="1"/>
+    <col min="43" max="43" width="20.625" hidden="1" customWidth="1"/>
+    <col min="44" max="47" width="41.125" customWidth="1"/>
+    <col min="48" max="48" width="23.625" customWidth="1"/>
     <col min="49" max="49" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -14421,7 +14682,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="3" spans="1:49" ht="213" customHeight="1" thickBot="1">
+    <row r="3" spans="1:49" ht="212.95" customHeight="1" thickBot="1">
       <c r="B3" s="198" t="str">
         <f>IF(OR(IF(COUNTIF(D6:AC69,"0")&lt;&gt;0,TRUE,FALSE),IF(COUNTIF(D6:AC69,"1")&lt;&gt;0,TRUE,FALSE)),"Search Table","Index Table")</f>
         <v>Index Table</v>
@@ -14515,7 +14776,7 @@
         <v>47</v>
       </c>
       <c r="AG3" s="286" t="s">
-        <v>234</v>
+        <v>272</v>
       </c>
       <c r="AH3" s="287"/>
       <c r="AI3" s="221" t="s">
@@ -14526,7 +14787,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="13.5" thickBot="1">
+    <row r="4" spans="1:49" ht="13.6" thickBot="1">
       <c r="A4" s="282" t="s">
         <v>63</v>
       </c>
@@ -14574,7 +14835,7 @@
       <c r="AV4" s="84"/>
       <c r="AW4" s="85"/>
     </row>
-    <row r="5" spans="1:49" ht="13.5" thickBot="1">
+    <row r="5" spans="1:49" ht="13.6" thickBot="1">
       <c r="A5" s="284"/>
       <c r="B5" s="285"/>
       <c r="C5" s="144"/>
@@ -15929,7 +16190,7 @@
         <v>1</v>
       </c>
       <c r="AJ15" s="218" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AL15" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -16091,7 +16352,7 @@
         <v>ALERT_VOM_BAT_WT</v>
       </c>
     </row>
-    <row r="17" spans="2:49" ht="13.5" thickBot="1">
+    <row r="17" spans="2:49" ht="13.6" thickBot="1">
       <c r="B17" s="140"/>
       <c r="C17" s="49">
         <f t="shared" si="2"/>
@@ -22471,7 +22732,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="13.5" thickBot="1">
+    <row r="70" spans="1:46" ht="13.6" thickBot="1">
       <c r="A70" s="58" t="s">
         <v>64</v>
       </c>
@@ -43094,24 +43355,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B2:Q15"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="2" max="2" width="35.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="10" width="3.36328125" customWidth="1"/>
-    <col min="11" max="11" width="19.453125" customWidth="1"/>
-    <col min="12" max="12" width="22.36328125" customWidth="1"/>
-    <col min="13" max="13" width="20.36328125" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" customWidth="1"/>
-    <col min="15" max="15" width="23.90625" customWidth="1"/>
-    <col min="16" max="17" width="10.90625" customWidth="1"/>
+    <col min="2" max="2" width="35.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="3.375" customWidth="1"/>
+    <col min="11" max="11" width="19.5" customWidth="1"/>
+    <col min="12" max="12" width="22.375" customWidth="1"/>
+    <col min="13" max="13" width="20.375" customWidth="1"/>
+    <col min="14" max="14" width="10.875" customWidth="1"/>
+    <col min="15" max="15" width="23.875" customWidth="1"/>
+    <col min="16" max="17" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" ht="14.5" thickBot="1">
+    <row r="2" spans="2:17" ht="15.65" thickBot="1">
       <c r="B2" s="27" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="3" spans="2:17" ht="14.5" thickBot="1">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="3" spans="2:17" ht="15.65" thickBot="1">
       <c r="B3" s="99" t="s">
         <v>165</v>
       </c>
@@ -43176,7 +43437,7 @@
       </c>
       <c r="L5" s="77"/>
       <c r="M5" s="31" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="N5" s="206" t="s">
         <v>23</v>
@@ -43233,7 +43494,7 @@
       <c r="P6" s="80"/>
       <c r="Q6" s="146"/>
     </row>
-    <row r="7" spans="2:17" ht="26">
+    <row r="7" spans="2:17" ht="25.85">
       <c r="B7" s="74" t="s">
         <v>27</v>
       </c>
@@ -43248,10 +43509,10 @@
       <c r="I7" s="211"/>
       <c r="J7" s="212"/>
       <c r="K7" s="28" t="s">
-        <v>233</v>
+        <v>273</v>
       </c>
       <c r="L7" s="28" t="s">
-        <v>233</v>
+        <v>273</v>
       </c>
       <c r="M7" s="32"/>
       <c r="N7" s="207"/>
@@ -43259,7 +43520,7 @@
       <c r="P7" s="80"/>
       <c r="Q7" s="146"/>
     </row>
-    <row r="8" spans="2:17" ht="131">
+    <row r="8" spans="2:17" ht="130.44999999999999">
       <c r="B8" s="73" t="s">
         <v>28</v>
       </c>
@@ -43288,7 +43549,7 @@
         <v>176</v>
       </c>
       <c r="K8" s="28" t="s">
-        <v>234</v>
+        <v>272</v>
       </c>
       <c r="L8" s="28" t="s">
         <v>232</v>
@@ -43301,7 +43562,7 @@
       <c r="P8" s="80"/>
       <c r="Q8" s="146"/>
     </row>
-    <row r="9" spans="2:17" ht="52.5" thickBot="1">
+    <row r="9" spans="2:17" ht="52.3" thickBot="1">
       <c r="B9" s="75" t="s">
         <v>30</v>
       </c>
@@ -43330,24 +43591,24 @@
         <v>178</v>
       </c>
       <c r="K9" s="29" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L9" s="29" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="M9" s="33" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="N9" s="208"/>
       <c r="O9" s="213" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="P9" s="220"/>
       <c r="Q9" s="147"/>
     </row>
-    <row r="10" spans="2:17" ht="13.5" thickTop="1">
+    <row r="10" spans="2:17" ht="13.6" thickTop="1">
       <c r="B10" s="76" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C10" s="176" t="s">
         <v>177</v>
@@ -43374,7 +43635,7 @@
         <v>177</v>
       </c>
       <c r="K10" s="37" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="L10" s="37" t="s">
         <v>230</v>
@@ -43391,7 +43652,7 @@
     </row>
     <row r="11" spans="2:17">
       <c r="B11" s="22" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C11" s="177" t="s">
         <v>177</v>
@@ -43418,24 +43679,24 @@
         <v>177</v>
       </c>
       <c r="K11" s="37" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="L11" s="36" t="s">
         <v>229</v>
       </c>
       <c r="M11" s="39" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="N11" s="177"/>
       <c r="O11" s="219" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="P11" s="43"/>
       <c r="Q11" s="149"/>
     </row>
     <row r="12" spans="2:17">
       <c r="B12" s="22" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C12" s="177" t="s">
         <v>177</v>
@@ -43462,10 +43723,10 @@
         <v>177</v>
       </c>
       <c r="K12" s="36" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="L12" s="36" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="M12" s="39" t="s">
         <v>32</v>
@@ -43479,7 +43740,7 @@
     </row>
     <row r="13" spans="2:17">
       <c r="B13" s="225" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C13" s="226" t="s">
         <v>177</v>
@@ -43506,10 +43767,10 @@
         <v>177</v>
       </c>
       <c r="K13" s="228" t="s">
+        <v>254</v>
+      </c>
+      <c r="L13" s="228" t="s">
         <v>256</v>
-      </c>
-      <c r="L13" s="228" t="s">
-        <v>258</v>
       </c>
       <c r="M13" s="229" t="s">
         <v>32</v>
@@ -43523,7 +43784,7 @@
     </row>
     <row r="14" spans="2:17">
       <c r="B14" s="225" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C14" s="226" t="s">
         <v>177</v>
@@ -43550,10 +43811,10 @@
         <v>177</v>
       </c>
       <c r="K14" s="228" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="L14" s="228" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="M14" s="229" t="s">
         <v>32</v>
@@ -43565,7 +43826,7 @@
       <c r="P14" s="231"/>
       <c r="Q14" s="232"/>
     </row>
-    <row r="15" spans="2:17" ht="13.5" thickBot="1">
+    <row r="15" spans="2:17" ht="13.6" thickBot="1">
       <c r="B15" s="23" t="s">
         <v>228</v>
       </c>
@@ -43594,10 +43855,10 @@
         <v>177</v>
       </c>
       <c r="K15" s="40" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="L15" s="40" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="M15" s="41" t="s">
         <v>32</v>
@@ -43629,14 +43890,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:D27"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="2" max="2" width="4.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.08984375" customWidth="1"/>
+    <col min="2" max="2" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.125" customWidth="1"/>
     <col min="4" max="4" width="86" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="13.5" thickBot="1">
+    <row r="2" spans="2:4" ht="13.6" thickBot="1">
       <c r="B2" s="87" t="s">
         <v>87</v>
       </c>
@@ -43646,7 +43907,7 @@
       </c>
       <c r="D2" s="88"/>
     </row>
-    <row r="3" spans="2:4" ht="13.5" thickBot="1">
+    <row r="3" spans="2:4" ht="13.6" thickBot="1">
       <c r="B3" s="81" t="s">
         <v>85</v>
       </c>
@@ -43657,7 +43918,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="13.5" thickTop="1">
+    <row r="4" spans="2:4" ht="13.6" thickTop="1">
       <c r="B4" s="12">
         <v>0</v>
       </c>
@@ -43668,7 +43929,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="39">
+    <row r="5" spans="2:4" ht="38.75">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -43679,7 +43940,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="26">
+    <row r="6" spans="2:4" ht="25.85">
       <c r="B6" s="2">
         <v>2</v>
       </c>
@@ -43690,7 +43951,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="52">
+    <row r="7" spans="2:4" ht="51.65">
       <c r="B7" s="2">
         <v>3</v>
       </c>
@@ -43701,7 +43962,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="78">
+    <row r="8" spans="2:4" ht="77.45">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -43712,7 +43973,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="41.25" customHeight="1">
+    <row r="9" spans="2:4" ht="41.3" customHeight="1">
       <c r="B9" s="2">
         <v>5</v>
       </c>
@@ -43723,7 +43984,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="26">
+    <row r="10" spans="2:4" ht="25.85">
       <c r="B10" s="2">
         <v>6</v>
       </c>
@@ -43734,7 +43995,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="26">
+    <row r="11" spans="2:4" ht="25.85">
       <c r="B11" s="2">
         <v>7</v>
       </c>
@@ -43745,7 +44006,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="26">
+    <row r="12" spans="2:4" ht="25.85">
       <c r="B12" s="2">
         <v>8</v>
       </c>
@@ -43756,7 +44017,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="26">
+    <row r="13" spans="2:4" ht="25.85">
       <c r="B13" s="2">
         <v>9</v>
       </c>
@@ -43767,7 +44028,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="26">
+    <row r="14" spans="2:4" ht="25.85">
       <c r="B14" s="2">
         <v>10</v>
       </c>
@@ -43778,7 +44039,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="130">
+    <row r="15" spans="2:4" ht="129.1">
       <c r="B15" s="2">
         <v>11</v>
       </c>
@@ -43800,7 +44061,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="26">
+    <row r="17" spans="2:4" ht="25.85">
       <c r="B17" s="2">
         <v>13</v>
       </c>
@@ -43811,7 +44072,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="91">
+    <row r="18" spans="2:4" ht="90.35">
       <c r="B18" s="2">
         <v>14</v>
       </c>
@@ -43822,7 +44083,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="39">
+    <row r="19" spans="2:4" ht="38.75">
       <c r="B19" s="2">
         <v>15</v>
       </c>
@@ -43833,7 +44094,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="20" spans="2:4" ht="64.5" customHeight="1">
+    <row r="20" spans="2:4" ht="64.55" customHeight="1">
       <c r="B20" s="2">
         <v>16</v>
       </c>
@@ -43855,7 +44116,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="26">
+    <row r="22" spans="2:4" ht="25.85">
       <c r="B22" s="2">
         <v>18</v>
       </c>
@@ -43866,7 +44127,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="23" spans="2:4" ht="26">
+    <row r="23" spans="2:4" ht="25.85">
       <c r="B23" s="2">
         <v>19</v>
       </c>
@@ -43877,15 +44138,15 @@
         <v>220</v>
       </c>
     </row>
-    <row r="24" spans="2:4" ht="91">
+    <row r="24" spans="2:4" ht="90.35">
       <c r="B24" s="2">
         <v>20</v>
       </c>
       <c r="C24" s="91" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D24" s="93" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="25" spans="2:4">
@@ -43898,7 +44159,7 @@
       <c r="C26" s="91"/>
       <c r="D26" s="78"/>
     </row>
-    <row r="27" spans="2:4" ht="13.5" thickBot="1">
+    <row r="27" spans="2:4" ht="13.6" thickBot="1">
       <c r="B27" s="3"/>
       <c r="C27" s="92"/>
       <c r="D27" s="5"/>
